--- a/Excel_files/momohara_neveu_2021_control.xlsx
+++ b/Excel_files/momohara_neveu_2021_control.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\SNNAPinNEURON\SingleNeuronFit\Excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D69D96-E732-4029-AF5F-7894FA91C0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EABE534-99AE-4112-9025-25B9DA53AC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" activeTab="3" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" activeTab="6" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
@@ -2236,13 +2236,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2260,22 +2260,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2314,46 +2329,31 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2377,16 +2377,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2394,6 +2391,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3687,329 +3687,329 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:303" x14ac:dyDescent="0.35">
-      <c r="E1" s="176" t="s">
+      <c r="E1" s="155" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="177"/>
-      <c r="G1" s="158" t="s">
+      <c r="F1" s="156"/>
+      <c r="G1" s="181" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
-      <c r="O1" s="159"/>
-      <c r="P1" s="159"/>
-      <c r="Q1" s="159"/>
-      <c r="R1" s="159"/>
-      <c r="S1" s="159"/>
-      <c r="T1" s="159"/>
-      <c r="U1" s="159"/>
-      <c r="V1" s="159"/>
-      <c r="W1" s="159"/>
-      <c r="X1" s="159"/>
-      <c r="Y1" s="159"/>
-      <c r="Z1" s="159"/>
-      <c r="AA1" s="159"/>
-      <c r="AB1" s="159"/>
-      <c r="AC1" s="159"/>
-      <c r="AD1" s="159"/>
-      <c r="AE1" s="159"/>
-      <c r="AF1" s="159"/>
-      <c r="AG1" s="160"/>
-      <c r="AH1" s="181" t="s">
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="182"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="182"/>
+      <c r="U1" s="182"/>
+      <c r="V1" s="182"/>
+      <c r="W1" s="182"/>
+      <c r="X1" s="182"/>
+      <c r="Y1" s="182"/>
+      <c r="Z1" s="182"/>
+      <c r="AA1" s="182"/>
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="182"/>
+      <c r="AD1" s="182"/>
+      <c r="AE1" s="182"/>
+      <c r="AF1" s="182"/>
+      <c r="AG1" s="183"/>
+      <c r="AH1" s="160" t="s">
         <v>93</v>
       </c>
-      <c r="AI1" s="182"/>
-      <c r="AJ1" s="182"/>
-      <c r="AK1" s="182"/>
-      <c r="AL1" s="182"/>
-      <c r="AM1" s="182"/>
-      <c r="AN1" s="182"/>
-      <c r="AO1" s="182"/>
-      <c r="AP1" s="182"/>
-      <c r="AQ1" s="182"/>
-      <c r="AR1" s="182"/>
-      <c r="AS1" s="182"/>
-      <c r="AT1" s="182"/>
-      <c r="AU1" s="182"/>
-      <c r="AV1" s="182"/>
-      <c r="AW1" s="182"/>
-      <c r="AX1" s="182"/>
-      <c r="AY1" s="182"/>
-      <c r="AZ1" s="182"/>
-      <c r="BA1" s="182"/>
-      <c r="BB1" s="182"/>
-      <c r="BC1" s="182"/>
-      <c r="BD1" s="182"/>
-      <c r="BE1" s="182"/>
-      <c r="BF1" s="182"/>
-      <c r="BG1" s="182"/>
-      <c r="BH1" s="183"/>
-      <c r="BI1" s="155" t="s">
+      <c r="AI1" s="161"/>
+      <c r="AJ1" s="161"/>
+      <c r="AK1" s="161"/>
+      <c r="AL1" s="161"/>
+      <c r="AM1" s="161"/>
+      <c r="AN1" s="161"/>
+      <c r="AO1" s="161"/>
+      <c r="AP1" s="161"/>
+      <c r="AQ1" s="161"/>
+      <c r="AR1" s="161"/>
+      <c r="AS1" s="161"/>
+      <c r="AT1" s="161"/>
+      <c r="AU1" s="161"/>
+      <c r="AV1" s="161"/>
+      <c r="AW1" s="161"/>
+      <c r="AX1" s="161"/>
+      <c r="AY1" s="161"/>
+      <c r="AZ1" s="161"/>
+      <c r="BA1" s="161"/>
+      <c r="BB1" s="161"/>
+      <c r="BC1" s="161"/>
+      <c r="BD1" s="161"/>
+      <c r="BE1" s="161"/>
+      <c r="BF1" s="161"/>
+      <c r="BG1" s="161"/>
+      <c r="BH1" s="162"/>
+      <c r="BI1" s="178" t="s">
         <v>139</v>
       </c>
-      <c r="BJ1" s="156"/>
-      <c r="BK1" s="156"/>
-      <c r="BL1" s="156"/>
-      <c r="BM1" s="156"/>
-      <c r="BN1" s="156"/>
-      <c r="BO1" s="156"/>
-      <c r="BP1" s="156"/>
-      <c r="BQ1" s="156"/>
-      <c r="BR1" s="156"/>
-      <c r="BS1" s="156"/>
-      <c r="BT1" s="156"/>
-      <c r="BU1" s="156"/>
-      <c r="BV1" s="156"/>
-      <c r="BW1" s="156"/>
-      <c r="BX1" s="156"/>
-      <c r="BY1" s="156"/>
-      <c r="BZ1" s="156"/>
-      <c r="CA1" s="156"/>
-      <c r="CB1" s="156"/>
-      <c r="CC1" s="156"/>
-      <c r="CD1" s="156"/>
-      <c r="CE1" s="156"/>
-      <c r="CF1" s="156"/>
-      <c r="CG1" s="156"/>
-      <c r="CH1" s="156"/>
-      <c r="CI1" s="157"/>
-      <c r="CJ1" s="184" t="s">
+      <c r="BJ1" s="179"/>
+      <c r="BK1" s="179"/>
+      <c r="BL1" s="179"/>
+      <c r="BM1" s="179"/>
+      <c r="BN1" s="179"/>
+      <c r="BO1" s="179"/>
+      <c r="BP1" s="179"/>
+      <c r="BQ1" s="179"/>
+      <c r="BR1" s="179"/>
+      <c r="BS1" s="179"/>
+      <c r="BT1" s="179"/>
+      <c r="BU1" s="179"/>
+      <c r="BV1" s="179"/>
+      <c r="BW1" s="179"/>
+      <c r="BX1" s="179"/>
+      <c r="BY1" s="179"/>
+      <c r="BZ1" s="179"/>
+      <c r="CA1" s="179"/>
+      <c r="CB1" s="179"/>
+      <c r="CC1" s="179"/>
+      <c r="CD1" s="179"/>
+      <c r="CE1" s="179"/>
+      <c r="CF1" s="179"/>
+      <c r="CG1" s="179"/>
+      <c r="CH1" s="179"/>
+      <c r="CI1" s="180"/>
+      <c r="CJ1" s="163" t="s">
         <v>137</v>
       </c>
-      <c r="CK1" s="185"/>
-      <c r="CL1" s="185"/>
-      <c r="CM1" s="185"/>
-      <c r="CN1" s="185"/>
-      <c r="CO1" s="185"/>
-      <c r="CP1" s="185"/>
-      <c r="CQ1" s="185"/>
-      <c r="CR1" s="185"/>
-      <c r="CS1" s="185"/>
-      <c r="CT1" s="185"/>
-      <c r="CU1" s="185"/>
-      <c r="CV1" s="185"/>
-      <c r="CW1" s="185"/>
-      <c r="CX1" s="185"/>
-      <c r="CY1" s="185"/>
-      <c r="CZ1" s="185"/>
-      <c r="DA1" s="185"/>
-      <c r="DB1" s="185"/>
-      <c r="DC1" s="185"/>
-      <c r="DD1" s="185"/>
-      <c r="DE1" s="185"/>
-      <c r="DF1" s="185"/>
-      <c r="DG1" s="185"/>
-      <c r="DH1" s="185"/>
-      <c r="DI1" s="185"/>
-      <c r="DJ1" s="186"/>
-      <c r="DK1" s="178" t="s">
+      <c r="CK1" s="164"/>
+      <c r="CL1" s="164"/>
+      <c r="CM1" s="164"/>
+      <c r="CN1" s="164"/>
+      <c r="CO1" s="164"/>
+      <c r="CP1" s="164"/>
+      <c r="CQ1" s="164"/>
+      <c r="CR1" s="164"/>
+      <c r="CS1" s="164"/>
+      <c r="CT1" s="164"/>
+      <c r="CU1" s="164"/>
+      <c r="CV1" s="164"/>
+      <c r="CW1" s="164"/>
+      <c r="CX1" s="164"/>
+      <c r="CY1" s="164"/>
+      <c r="CZ1" s="164"/>
+      <c r="DA1" s="164"/>
+      <c r="DB1" s="164"/>
+      <c r="DC1" s="164"/>
+      <c r="DD1" s="164"/>
+      <c r="DE1" s="164"/>
+      <c r="DF1" s="164"/>
+      <c r="DG1" s="164"/>
+      <c r="DH1" s="164"/>
+      <c r="DI1" s="164"/>
+      <c r="DJ1" s="165"/>
+      <c r="DK1" s="157" t="s">
         <v>138</v>
       </c>
-      <c r="DL1" s="179"/>
-      <c r="DM1" s="179"/>
-      <c r="DN1" s="179"/>
-      <c r="DO1" s="179"/>
-      <c r="DP1" s="179"/>
-      <c r="DQ1" s="179"/>
-      <c r="DR1" s="179"/>
-      <c r="DS1" s="179"/>
-      <c r="DT1" s="179"/>
-      <c r="DU1" s="179"/>
-      <c r="DV1" s="179"/>
-      <c r="DW1" s="179"/>
-      <c r="DX1" s="179"/>
-      <c r="DY1" s="179"/>
-      <c r="DZ1" s="179"/>
-      <c r="EA1" s="179"/>
-      <c r="EB1" s="179"/>
-      <c r="EC1" s="179"/>
-      <c r="ED1" s="179"/>
-      <c r="EE1" s="179"/>
-      <c r="EF1" s="179"/>
-      <c r="EG1" s="179"/>
-      <c r="EH1" s="179"/>
-      <c r="EI1" s="179"/>
-      <c r="EJ1" s="179"/>
-      <c r="EK1" s="180"/>
-      <c r="EL1" s="170" t="s">
+      <c r="DL1" s="158"/>
+      <c r="DM1" s="158"/>
+      <c r="DN1" s="158"/>
+      <c r="DO1" s="158"/>
+      <c r="DP1" s="158"/>
+      <c r="DQ1" s="158"/>
+      <c r="DR1" s="158"/>
+      <c r="DS1" s="158"/>
+      <c r="DT1" s="158"/>
+      <c r="DU1" s="158"/>
+      <c r="DV1" s="158"/>
+      <c r="DW1" s="158"/>
+      <c r="DX1" s="158"/>
+      <c r="DY1" s="158"/>
+      <c r="DZ1" s="158"/>
+      <c r="EA1" s="158"/>
+      <c r="EB1" s="158"/>
+      <c r="EC1" s="158"/>
+      <c r="ED1" s="158"/>
+      <c r="EE1" s="158"/>
+      <c r="EF1" s="158"/>
+      <c r="EG1" s="158"/>
+      <c r="EH1" s="158"/>
+      <c r="EI1" s="158"/>
+      <c r="EJ1" s="158"/>
+      <c r="EK1" s="159"/>
+      <c r="EL1" s="175" t="s">
         <v>160</v>
       </c>
-      <c r="EM1" s="171"/>
-      <c r="EN1" s="171"/>
-      <c r="EO1" s="171"/>
-      <c r="EP1" s="171"/>
-      <c r="EQ1" s="171"/>
-      <c r="ER1" s="171"/>
-      <c r="ES1" s="171"/>
-      <c r="ET1" s="171"/>
-      <c r="EU1" s="171"/>
-      <c r="EV1" s="171"/>
-      <c r="EW1" s="171"/>
-      <c r="EX1" s="171"/>
-      <c r="EY1" s="171"/>
-      <c r="EZ1" s="171"/>
-      <c r="FA1" s="171"/>
-      <c r="FB1" s="171"/>
-      <c r="FC1" s="171"/>
-      <c r="FD1" s="171"/>
-      <c r="FE1" s="171"/>
-      <c r="FF1" s="171"/>
-      <c r="FG1" s="171"/>
-      <c r="FH1" s="171"/>
-      <c r="FI1" s="171"/>
-      <c r="FJ1" s="171"/>
-      <c r="FK1" s="171"/>
-      <c r="FL1" s="172"/>
-      <c r="FM1" s="164" t="s">
+      <c r="EM1" s="176"/>
+      <c r="EN1" s="176"/>
+      <c r="EO1" s="176"/>
+      <c r="EP1" s="176"/>
+      <c r="EQ1" s="176"/>
+      <c r="ER1" s="176"/>
+      <c r="ES1" s="176"/>
+      <c r="ET1" s="176"/>
+      <c r="EU1" s="176"/>
+      <c r="EV1" s="176"/>
+      <c r="EW1" s="176"/>
+      <c r="EX1" s="176"/>
+      <c r="EY1" s="176"/>
+      <c r="EZ1" s="176"/>
+      <c r="FA1" s="176"/>
+      <c r="FB1" s="176"/>
+      <c r="FC1" s="176"/>
+      <c r="FD1" s="176"/>
+      <c r="FE1" s="176"/>
+      <c r="FF1" s="176"/>
+      <c r="FG1" s="176"/>
+      <c r="FH1" s="176"/>
+      <c r="FI1" s="176"/>
+      <c r="FJ1" s="176"/>
+      <c r="FK1" s="176"/>
+      <c r="FL1" s="177"/>
+      <c r="FM1" s="169" t="s">
         <v>211</v>
       </c>
-      <c r="FN1" s="165"/>
-      <c r="FO1" s="165"/>
-      <c r="FP1" s="165"/>
-      <c r="FQ1" s="165"/>
-      <c r="FR1" s="165"/>
-      <c r="FS1" s="165"/>
-      <c r="FT1" s="165"/>
-      <c r="FU1" s="165"/>
-      <c r="FV1" s="165"/>
-      <c r="FW1" s="165"/>
-      <c r="FX1" s="165"/>
-      <c r="FY1" s="165"/>
-      <c r="FZ1" s="165"/>
-      <c r="GA1" s="165"/>
-      <c r="GB1" s="165"/>
-      <c r="GC1" s="165"/>
-      <c r="GD1" s="165"/>
-      <c r="GE1" s="165"/>
-      <c r="GF1" s="165"/>
-      <c r="GG1" s="165"/>
-      <c r="GH1" s="165"/>
-      <c r="GI1" s="165"/>
-      <c r="GJ1" s="165"/>
-      <c r="GK1" s="165"/>
-      <c r="GL1" s="165"/>
-      <c r="GM1" s="166"/>
-      <c r="GN1" s="147" t="s">
+      <c r="FN1" s="170"/>
+      <c r="FO1" s="170"/>
+      <c r="FP1" s="170"/>
+      <c r="FQ1" s="170"/>
+      <c r="FR1" s="170"/>
+      <c r="FS1" s="170"/>
+      <c r="FT1" s="170"/>
+      <c r="FU1" s="170"/>
+      <c r="FV1" s="170"/>
+      <c r="FW1" s="170"/>
+      <c r="FX1" s="170"/>
+      <c r="FY1" s="170"/>
+      <c r="FZ1" s="170"/>
+      <c r="GA1" s="170"/>
+      <c r="GB1" s="170"/>
+      <c r="GC1" s="170"/>
+      <c r="GD1" s="170"/>
+      <c r="GE1" s="170"/>
+      <c r="GF1" s="170"/>
+      <c r="GG1" s="170"/>
+      <c r="GH1" s="170"/>
+      <c r="GI1" s="170"/>
+      <c r="GJ1" s="170"/>
+      <c r="GK1" s="170"/>
+      <c r="GL1" s="170"/>
+      <c r="GM1" s="171"/>
+      <c r="GN1" s="184" t="s">
         <v>161</v>
       </c>
-      <c r="GO1" s="148"/>
-      <c r="GP1" s="148"/>
-      <c r="GQ1" s="148"/>
-      <c r="GR1" s="148"/>
-      <c r="GS1" s="148"/>
-      <c r="GT1" s="148"/>
-      <c r="GU1" s="148"/>
-      <c r="GV1" s="148"/>
-      <c r="GW1" s="148"/>
-      <c r="GX1" s="148"/>
-      <c r="GY1" s="148"/>
-      <c r="GZ1" s="148"/>
-      <c r="HA1" s="148"/>
-      <c r="HB1" s="148"/>
-      <c r="HC1" s="148"/>
-      <c r="HD1" s="148"/>
-      <c r="HE1" s="148"/>
-      <c r="HF1" s="148"/>
-      <c r="HG1" s="148"/>
-      <c r="HH1" s="148"/>
-      <c r="HI1" s="148"/>
-      <c r="HJ1" s="148"/>
-      <c r="HK1" s="148"/>
-      <c r="HL1" s="148"/>
-      <c r="HM1" s="148"/>
-      <c r="HN1" s="149"/>
-      <c r="HO1" s="167" t="s">
+      <c r="GO1" s="185"/>
+      <c r="GP1" s="185"/>
+      <c r="GQ1" s="185"/>
+      <c r="GR1" s="185"/>
+      <c r="GS1" s="185"/>
+      <c r="GT1" s="185"/>
+      <c r="GU1" s="185"/>
+      <c r="GV1" s="185"/>
+      <c r="GW1" s="185"/>
+      <c r="GX1" s="185"/>
+      <c r="GY1" s="185"/>
+      <c r="GZ1" s="185"/>
+      <c r="HA1" s="185"/>
+      <c r="HB1" s="185"/>
+      <c r="HC1" s="185"/>
+      <c r="HD1" s="185"/>
+      <c r="HE1" s="185"/>
+      <c r="HF1" s="185"/>
+      <c r="HG1" s="185"/>
+      <c r="HH1" s="185"/>
+      <c r="HI1" s="185"/>
+      <c r="HJ1" s="185"/>
+      <c r="HK1" s="185"/>
+      <c r="HL1" s="185"/>
+      <c r="HM1" s="185"/>
+      <c r="HN1" s="186"/>
+      <c r="HO1" s="172" t="s">
         <v>140</v>
       </c>
-      <c r="HP1" s="168"/>
-      <c r="HQ1" s="168"/>
-      <c r="HR1" s="168"/>
-      <c r="HS1" s="168"/>
-      <c r="HT1" s="168"/>
-      <c r="HU1" s="168"/>
-      <c r="HV1" s="168"/>
-      <c r="HW1" s="168"/>
-      <c r="HX1" s="168"/>
-      <c r="HY1" s="168"/>
-      <c r="HZ1" s="168"/>
-      <c r="IA1" s="168"/>
-      <c r="IB1" s="168"/>
-      <c r="IC1" s="168"/>
-      <c r="ID1" s="168"/>
-      <c r="IE1" s="168"/>
-      <c r="IF1" s="168"/>
-      <c r="IG1" s="168"/>
-      <c r="IH1" s="168"/>
-      <c r="II1" s="168"/>
-      <c r="IJ1" s="168"/>
-      <c r="IK1" s="168"/>
-      <c r="IL1" s="168"/>
-      <c r="IM1" s="168"/>
-      <c r="IN1" s="168"/>
-      <c r="IO1" s="169"/>
-      <c r="IP1" s="161" t="s">
+      <c r="HP1" s="173"/>
+      <c r="HQ1" s="173"/>
+      <c r="HR1" s="173"/>
+      <c r="HS1" s="173"/>
+      <c r="HT1" s="173"/>
+      <c r="HU1" s="173"/>
+      <c r="HV1" s="173"/>
+      <c r="HW1" s="173"/>
+      <c r="HX1" s="173"/>
+      <c r="HY1" s="173"/>
+      <c r="HZ1" s="173"/>
+      <c r="IA1" s="173"/>
+      <c r="IB1" s="173"/>
+      <c r="IC1" s="173"/>
+      <c r="ID1" s="173"/>
+      <c r="IE1" s="173"/>
+      <c r="IF1" s="173"/>
+      <c r="IG1" s="173"/>
+      <c r="IH1" s="173"/>
+      <c r="II1" s="173"/>
+      <c r="IJ1" s="173"/>
+      <c r="IK1" s="173"/>
+      <c r="IL1" s="173"/>
+      <c r="IM1" s="173"/>
+      <c r="IN1" s="173"/>
+      <c r="IO1" s="174"/>
+      <c r="IP1" s="166" t="s">
         <v>146</v>
       </c>
-      <c r="IQ1" s="162"/>
-      <c r="IR1" s="162"/>
-      <c r="IS1" s="162"/>
-      <c r="IT1" s="162"/>
-      <c r="IU1" s="162"/>
-      <c r="IV1" s="162"/>
-      <c r="IW1" s="162"/>
-      <c r="IX1" s="162"/>
-      <c r="IY1" s="162"/>
-      <c r="IZ1" s="162"/>
-      <c r="JA1" s="162"/>
-      <c r="JB1" s="162"/>
-      <c r="JC1" s="162"/>
-      <c r="JD1" s="162"/>
-      <c r="JE1" s="162"/>
-      <c r="JF1" s="162"/>
-      <c r="JG1" s="162"/>
-      <c r="JH1" s="162"/>
-      <c r="JI1" s="162"/>
-      <c r="JJ1" s="162"/>
-      <c r="JK1" s="162"/>
-      <c r="JL1" s="162"/>
-      <c r="JM1" s="162"/>
-      <c r="JN1" s="162"/>
-      <c r="JO1" s="162"/>
-      <c r="JP1" s="163"/>
-      <c r="JQ1" s="173" t="s">
+      <c r="IQ1" s="167"/>
+      <c r="IR1" s="167"/>
+      <c r="IS1" s="167"/>
+      <c r="IT1" s="167"/>
+      <c r="IU1" s="167"/>
+      <c r="IV1" s="167"/>
+      <c r="IW1" s="167"/>
+      <c r="IX1" s="167"/>
+      <c r="IY1" s="167"/>
+      <c r="IZ1" s="167"/>
+      <c r="JA1" s="167"/>
+      <c r="JB1" s="167"/>
+      <c r="JC1" s="167"/>
+      <c r="JD1" s="167"/>
+      <c r="JE1" s="167"/>
+      <c r="JF1" s="167"/>
+      <c r="JG1" s="167"/>
+      <c r="JH1" s="167"/>
+      <c r="JI1" s="167"/>
+      <c r="JJ1" s="167"/>
+      <c r="JK1" s="167"/>
+      <c r="JL1" s="167"/>
+      <c r="JM1" s="167"/>
+      <c r="JN1" s="167"/>
+      <c r="JO1" s="167"/>
+      <c r="JP1" s="168"/>
+      <c r="JQ1" s="147" t="s">
         <v>182</v>
       </c>
-      <c r="JR1" s="174"/>
-      <c r="JS1" s="174"/>
-      <c r="JT1" s="174"/>
-      <c r="JU1" s="174"/>
-      <c r="JV1" s="174"/>
-      <c r="JW1" s="174"/>
-      <c r="JX1" s="174"/>
-      <c r="JY1" s="174"/>
-      <c r="JZ1" s="174"/>
-      <c r="KA1" s="174"/>
-      <c r="KB1" s="174"/>
-      <c r="KC1" s="174"/>
-      <c r="KD1" s="174"/>
-      <c r="KE1" s="174"/>
-      <c r="KF1" s="174"/>
-      <c r="KG1" s="174"/>
-      <c r="KH1" s="174"/>
-      <c r="KI1" s="174"/>
-      <c r="KJ1" s="174"/>
-      <c r="KK1" s="174"/>
-      <c r="KL1" s="174"/>
-      <c r="KM1" s="174"/>
-      <c r="KN1" s="174"/>
-      <c r="KO1" s="174"/>
-      <c r="KP1" s="174"/>
-      <c r="KQ1" s="175"/>
+      <c r="JR1" s="148"/>
+      <c r="JS1" s="148"/>
+      <c r="JT1" s="148"/>
+      <c r="JU1" s="148"/>
+      <c r="JV1" s="148"/>
+      <c r="JW1" s="148"/>
+      <c r="JX1" s="148"/>
+      <c r="JY1" s="148"/>
+      <c r="JZ1" s="148"/>
+      <c r="KA1" s="148"/>
+      <c r="KB1" s="148"/>
+      <c r="KC1" s="148"/>
+      <c r="KD1" s="148"/>
+      <c r="KE1" s="148"/>
+      <c r="KF1" s="148"/>
+      <c r="KG1" s="148"/>
+      <c r="KH1" s="148"/>
+      <c r="KI1" s="148"/>
+      <c r="KJ1" s="148"/>
+      <c r="KK1" s="148"/>
+      <c r="KL1" s="148"/>
+      <c r="KM1" s="148"/>
+      <c r="KN1" s="148"/>
+      <c r="KO1" s="148"/>
+      <c r="KP1" s="148"/>
+      <c r="KQ1" s="149"/>
     </row>
     <row r="2" spans="1:303" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D2" s="56" t="s">
@@ -15736,6 +15736,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="GN1:HN1"/>
+    <mergeCell ref="GN2:GP2"/>
+    <mergeCell ref="GQ2:HB2"/>
+    <mergeCell ref="HC2:HN2"/>
+    <mergeCell ref="CJ2:CL2"/>
+    <mergeCell ref="CM2:CX2"/>
+    <mergeCell ref="CY2:DJ2"/>
+    <mergeCell ref="BI1:CI1"/>
+    <mergeCell ref="FA2:FL2"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="G1:AG1"/>
+    <mergeCell ref="BI2:BK2"/>
+    <mergeCell ref="BL2:BW2"/>
+    <mergeCell ref="IP1:JP1"/>
+    <mergeCell ref="IP2:IR2"/>
+    <mergeCell ref="IS2:JD2"/>
+    <mergeCell ref="JE2:JP2"/>
+    <mergeCell ref="BX2:CI2"/>
+    <mergeCell ref="FM1:GM1"/>
+    <mergeCell ref="FM2:FO2"/>
+    <mergeCell ref="FP2:GA2"/>
+    <mergeCell ref="GB2:GM2"/>
+    <mergeCell ref="HO1:IO1"/>
+    <mergeCell ref="HO2:HQ2"/>
+    <mergeCell ref="HR2:IC2"/>
+    <mergeCell ref="ID2:IO2"/>
+    <mergeCell ref="EL1:FL1"/>
+    <mergeCell ref="EL2:EN2"/>
+    <mergeCell ref="EO2:EZ2"/>
     <mergeCell ref="JQ1:KQ1"/>
     <mergeCell ref="JQ2:JS2"/>
     <mergeCell ref="JT2:KE2"/>
@@ -15752,36 +15782,6 @@
     <mergeCell ref="AK2:AV2"/>
     <mergeCell ref="AW2:BH2"/>
     <mergeCell ref="CJ1:DJ1"/>
-    <mergeCell ref="IP1:JP1"/>
-    <mergeCell ref="IP2:IR2"/>
-    <mergeCell ref="IS2:JD2"/>
-    <mergeCell ref="JE2:JP2"/>
-    <mergeCell ref="BX2:CI2"/>
-    <mergeCell ref="FM1:GM1"/>
-    <mergeCell ref="FM2:FO2"/>
-    <mergeCell ref="FP2:GA2"/>
-    <mergeCell ref="GB2:GM2"/>
-    <mergeCell ref="HO1:IO1"/>
-    <mergeCell ref="HO2:HQ2"/>
-    <mergeCell ref="HR2:IC2"/>
-    <mergeCell ref="ID2:IO2"/>
-    <mergeCell ref="EL1:FL1"/>
-    <mergeCell ref="EL2:EN2"/>
-    <mergeCell ref="EO2:EZ2"/>
-    <mergeCell ref="BI1:CI1"/>
-    <mergeCell ref="FA2:FL2"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="G1:AG1"/>
-    <mergeCell ref="BI2:BK2"/>
-    <mergeCell ref="BL2:BW2"/>
-    <mergeCell ref="GN1:HN1"/>
-    <mergeCell ref="GN2:GP2"/>
-    <mergeCell ref="GQ2:HB2"/>
-    <mergeCell ref="HC2:HN2"/>
-    <mergeCell ref="CJ2:CL2"/>
-    <mergeCell ref="CM2:CX2"/>
-    <mergeCell ref="CY2:DJ2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A24">
     <cfRule type="cellIs" dxfId="48" priority="107" operator="equal">
@@ -16151,7 +16151,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="176" t="s">
+      <c r="B7" s="155" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="187"/>
@@ -16164,28 +16164,28 @@
       <c r="H7" s="187"/>
       <c r="I7" s="187"/>
       <c r="J7" s="187"/>
-      <c r="K7" s="177"/>
-      <c r="L7" s="176" t="s">
+      <c r="K7" s="156"/>
+      <c r="L7" s="155" t="s">
         <v>41</v>
       </c>
       <c r="M7" s="187"/>
       <c r="N7" s="187"/>
       <c r="O7" s="187"/>
-      <c r="P7" s="177"/>
-      <c r="Q7" s="176" t="s">
+      <c r="P7" s="156"/>
+      <c r="Q7" s="155" t="s">
         <v>42</v>
       </c>
       <c r="R7" s="187"/>
       <c r="S7" s="187"/>
       <c r="T7" s="187"/>
-      <c r="U7" s="177"/>
-      <c r="V7" s="176" t="s">
+      <c r="U7" s="156"/>
+      <c r="V7" s="155" t="s">
         <v>43</v>
       </c>
       <c r="W7" s="187"/>
       <c r="X7" s="187"/>
       <c r="Y7" s="187"/>
-      <c r="Z7" s="177"/>
+      <c r="Z7" s="156"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="47" t="s">
@@ -18137,7 +18137,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="176" t="s">
+      <c r="B7" s="155" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="187"/>
@@ -18150,28 +18150,28 @@
       <c r="H7" s="187"/>
       <c r="I7" s="187"/>
       <c r="J7" s="187"/>
-      <c r="K7" s="177"/>
-      <c r="L7" s="176" t="s">
+      <c r="K7" s="156"/>
+      <c r="L7" s="155" t="s">
         <v>41</v>
       </c>
       <c r="M7" s="187"/>
       <c r="N7" s="187"/>
       <c r="O7" s="187"/>
-      <c r="P7" s="177"/>
-      <c r="Q7" s="176" t="s">
+      <c r="P7" s="156"/>
+      <c r="Q7" s="155" t="s">
         <v>42</v>
       </c>
       <c r="R7" s="187"/>
       <c r="S7" s="187"/>
       <c r="T7" s="187"/>
-      <c r="U7" s="177"/>
-      <c r="V7" s="176" t="s">
+      <c r="U7" s="156"/>
+      <c r="V7" s="155" t="s">
         <v>43</v>
       </c>
       <c r="W7" s="187"/>
       <c r="X7" s="187"/>
       <c r="Y7" s="187"/>
-      <c r="Z7" s="177"/>
+      <c r="Z7" s="156"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="47" t="s">
@@ -19705,17 +19705,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="M27:Q28"/>
     <mergeCell ref="V7:Z7"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="L7:P7"/>
     <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="M27:Q28"/>
   </mergeCells>
   <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" dxfId="17" priority="208" operator="notEqual">
@@ -19767,35 +19767,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="198"/>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198" t="s">
+      <c r="A1" s="197"/>
+      <c r="B1" s="197"/>
+      <c r="C1" s="197" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="198"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="198"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="198"/>
-      <c r="O1" s="198"/>
-      <c r="P1" s="198"/>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
     </row>
     <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="198"/>
-      <c r="B2" s="198"/>
+      <c r="A2" s="197"/>
+      <c r="B2" s="197"/>
       <c r="C2" s="135" t="str">
         <f>Neu!$B4</f>
         <v>B4</v>
@@ -19882,10 +19882,10 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="199" t="s">
+      <c r="A3" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="197" t="str">
+      <c r="B3" s="194" t="str">
         <f>Neu!B4</f>
         <v>B4</v>
       </c>
@@ -19933,7 +19933,7 @@
       <c r="AD3" s="70"/>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="199"/>
+      <c r="A4" s="198"/>
       <c r="B4" s="195"/>
       <c r="C4" s="124"/>
       <c r="D4" s="118"/>
@@ -19970,8 +19970,8 @@
       <c r="AD4" s="70"/>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="199"/>
-      <c r="B5" s="194" t="str">
+      <c r="A5" s="198"/>
+      <c r="B5" s="196" t="str">
         <f>Neu!B5</f>
         <v>B8</v>
       </c>
@@ -20008,7 +20008,7 @@
       <c r="AD5" s="70"/>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="199"/>
+      <c r="A6" s="198"/>
       <c r="B6" s="195"/>
       <c r="C6" s="128"/>
       <c r="D6" s="119"/>
@@ -20043,8 +20043,8 @@
       <c r="AD6" s="70"/>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="199"/>
-      <c r="B7" s="194" t="str">
+      <c r="A7" s="198"/>
+      <c r="B7" s="196" t="str">
         <f>Neu!B6</f>
         <v>B20</v>
       </c>
@@ -20085,7 +20085,7 @@
       <c r="AD7" s="70"/>
     </row>
     <row r="8" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="199"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="195"/>
       <c r="C8" s="128">
         <v>0.18</v>
@@ -20124,8 +20124,8 @@
       <c r="AD8" s="70"/>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="199"/>
-      <c r="B9" s="194" t="str">
+      <c r="A9" s="198"/>
+      <c r="B9" s="196" t="str">
         <f>Neu!B7</f>
         <v>B30</v>
       </c>
@@ -20170,7 +20170,7 @@
       <c r="AD9" s="70"/>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="199"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="195"/>
       <c r="C10" s="128"/>
       <c r="D10" s="103">
@@ -20209,8 +20209,8 @@
       <c r="AD10" s="70"/>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="199"/>
-      <c r="B11" s="194" t="str">
+      <c r="A11" s="198"/>
+      <c r="B11" s="196" t="str">
         <f>Neu!B8</f>
         <v>B31s</v>
       </c>
@@ -20247,7 +20247,7 @@
       <c r="AD11" s="70"/>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="199"/>
+      <c r="A12" s="198"/>
       <c r="B12" s="195"/>
       <c r="C12" s="128"/>
       <c r="D12" s="103"/>
@@ -20282,8 +20282,8 @@
       <c r="AD12" s="70"/>
     </row>
     <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="199"/>
-      <c r="B13" s="194" t="str">
+      <c r="A13" s="198"/>
+      <c r="B13" s="196" t="str">
         <f>Neu!B9</f>
         <v>B31a</v>
       </c>
@@ -20322,7 +20322,7 @@
       <c r="AD13" s="70"/>
     </row>
     <row r="14" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="199"/>
+      <c r="A14" s="198"/>
       <c r="B14" s="195"/>
       <c r="C14" s="129"/>
       <c r="D14" s="118"/>
@@ -20359,8 +20359,8 @@
       <c r="AD14" s="70"/>
     </row>
     <row r="15" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="199"/>
-      <c r="B15" s="194" t="str">
+      <c r="A15" s="198"/>
+      <c r="B15" s="196" t="str">
         <f>Neu!B10</f>
         <v>B34</v>
       </c>
@@ -20407,7 +20407,7 @@
       <c r="AD15" s="70"/>
     </row>
     <row r="16" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="199"/>
+      <c r="A16" s="198"/>
       <c r="B16" s="195"/>
       <c r="C16" s="128"/>
       <c r="D16" s="103">
@@ -20446,8 +20446,8 @@
       <c r="AD16" s="70"/>
     </row>
     <row r="17" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="199"/>
-      <c r="B17" s="194" t="str">
+      <c r="A17" s="198"/>
+      <c r="B17" s="196" t="str">
         <f>Neu!B11</f>
         <v>B35</v>
       </c>
@@ -20490,7 +20490,7 @@
       <c r="AD17" s="70"/>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="199"/>
+      <c r="A18" s="198"/>
       <c r="B18" s="195"/>
       <c r="C18" s="128">
         <v>1.3</v>
@@ -20529,8 +20529,8 @@
       <c r="AD18" s="70"/>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="199"/>
-      <c r="B19" s="194" t="str">
+      <c r="A19" s="198"/>
+      <c r="B19" s="196" t="str">
         <f>Neu!B12</f>
         <v>B40</v>
       </c>
@@ -20573,7 +20573,7 @@
       <c r="AD19" s="70"/>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="199"/>
+      <c r="A20" s="198"/>
       <c r="B20" s="195"/>
       <c r="C20" s="128"/>
       <c r="D20" s="103">
@@ -20610,8 +20610,8 @@
       <c r="AD20" s="70"/>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="199"/>
-      <c r="B21" s="194" t="str">
+      <c r="A21" s="198"/>
+      <c r="B21" s="196" t="str">
         <f>Neu!B13</f>
         <v>B51s</v>
       </c>
@@ -20648,7 +20648,7 @@
       <c r="AD21" s="70"/>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="199"/>
+      <c r="A22" s="198"/>
       <c r="B22" s="195"/>
       <c r="C22" s="128"/>
       <c r="D22" s="103"/>
@@ -20683,8 +20683,8 @@
       <c r="AD22" s="70"/>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="199"/>
-      <c r="B23" s="194" t="str">
+      <c r="A23" s="198"/>
+      <c r="B23" s="196" t="str">
         <f>Neu!B14</f>
         <v>B51a</v>
       </c>
@@ -20727,7 +20727,7 @@
       <c r="AD23" s="70"/>
     </row>
     <row r="24" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="199"/>
+      <c r="A24" s="198"/>
       <c r="B24" s="195"/>
       <c r="C24" s="129"/>
       <c r="D24" s="118"/>
@@ -20762,8 +20762,8 @@
       <c r="AD24" s="70"/>
     </row>
     <row r="25" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="199"/>
-      <c r="B25" s="194" t="str">
+      <c r="A25" s="198"/>
+      <c r="B25" s="196" t="str">
         <f>Neu!B15</f>
         <v>B52</v>
       </c>
@@ -20806,7 +20806,7 @@
       <c r="AD25" s="70"/>
     </row>
     <row r="26" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="199"/>
+      <c r="A26" s="198"/>
       <c r="B26" s="195"/>
       <c r="C26" s="128"/>
       <c r="D26" s="103"/>
@@ -20843,8 +20843,8 @@
       <c r="AD26" s="70"/>
     </row>
     <row r="27" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="199"/>
-      <c r="B27" s="194" t="str">
+      <c r="A27" s="198"/>
+      <c r="B27" s="196" t="str">
         <f>Neu!B16</f>
         <v>B63</v>
       </c>
@@ -20890,7 +20890,7 @@
       <c r="AD27" s="70"/>
     </row>
     <row r="28" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="199"/>
+      <c r="A28" s="198"/>
       <c r="B28" s="195"/>
       <c r="C28" s="128"/>
       <c r="D28" s="103"/>
@@ -20930,8 +20930,8 @@
       <c r="AD28" s="70"/>
     </row>
     <row r="29" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="199"/>
-      <c r="B29" s="194" t="str">
+      <c r="A29" s="198"/>
+      <c r="B29" s="196" t="str">
         <f>Neu!B17</f>
         <v>B64s</v>
       </c>
@@ -20965,7 +20965,7 @@
       <c r="AD29" s="70"/>
     </row>
     <row r="30" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="199"/>
+      <c r="A30" s="198"/>
       <c r="B30" s="195"/>
       <c r="C30" s="129"/>
       <c r="D30" s="118"/>
@@ -20997,8 +20997,8 @@
       <c r="AD30" s="70"/>
     </row>
     <row r="31" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="199"/>
-      <c r="B31" s="194" t="str">
+      <c r="A31" s="198"/>
+      <c r="B31" s="196" t="str">
         <f>Neu!B18</f>
         <v>B64a</v>
       </c>
@@ -21058,7 +21058,7 @@
       <c r="AD31" s="70"/>
     </row>
     <row r="32" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="199"/>
+      <c r="A32" s="198"/>
       <c r="B32" s="195"/>
       <c r="C32" s="128"/>
       <c r="D32" s="103"/>
@@ -21090,8 +21090,8 @@
       <c r="AD32" s="70"/>
     </row>
     <row r="33" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="199"/>
-      <c r="B33" s="194" t="str">
+      <c r="A33" s="198"/>
+      <c r="B33" s="196" t="str">
         <f>Neu!B19</f>
         <v>B65</v>
       </c>
@@ -21139,7 +21139,7 @@
       <c r="AD33" s="70"/>
     </row>
     <row r="34" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="199"/>
+      <c r="A34" s="198"/>
       <c r="B34" s="195"/>
       <c r="C34" s="128"/>
       <c r="D34" s="103">
@@ -21179,8 +21179,8 @@
       <c r="AD34" s="70"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="199"/>
-      <c r="B35" s="194" t="str">
+      <c r="A35" s="198"/>
+      <c r="B35" s="196" t="str">
         <f>Neu!B20</f>
         <v>CBI2</v>
       </c>
@@ -21222,7 +21222,7 @@
       <c r="AD35" s="70"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="199"/>
+      <c r="A36" s="198"/>
       <c r="B36" s="195"/>
       <c r="C36" s="128"/>
       <c r="D36" s="103">
@@ -21266,8 +21266,8 @@
       <c r="AD36" s="70"/>
     </row>
     <row r="37" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="199"/>
-      <c r="B37" s="194">
+      <c r="A37" s="198"/>
+      <c r="B37" s="196">
         <f>Neu!B21</f>
         <v>0</v>
       </c>
@@ -21301,7 +21301,7 @@
       <c r="AD37" s="70"/>
     </row>
     <row r="38" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="199"/>
+      <c r="A38" s="198"/>
       <c r="B38" s="195"/>
       <c r="C38" s="129"/>
       <c r="D38" s="118"/>
@@ -21333,8 +21333,8 @@
       <c r="AD38" s="70"/>
     </row>
     <row r="39" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="199"/>
-      <c r="B39" s="194">
+      <c r="A39" s="198"/>
+      <c r="B39" s="196">
         <f>Neu!B22</f>
         <v>0</v>
       </c>
@@ -21368,7 +21368,7 @@
       <c r="AD39" s="70"/>
     </row>
     <row r="40" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="199"/>
+      <c r="A40" s="198"/>
       <c r="B40" s="195"/>
       <c r="C40" s="128"/>
       <c r="D40" s="103"/>
@@ -21400,8 +21400,8 @@
       <c r="AD40" s="70"/>
     </row>
     <row r="41" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="199"/>
-      <c r="B41" s="194">
+      <c r="A41" s="198"/>
+      <c r="B41" s="196">
         <f>Neu!B23</f>
         <v>0</v>
       </c>
@@ -21435,7 +21435,7 @@
       <c r="AD41" s="70"/>
     </row>
     <row r="42" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="199"/>
+      <c r="A42" s="198"/>
       <c r="B42" s="195"/>
       <c r="C42" s="128"/>
       <c r="D42" s="103"/>
@@ -21467,8 +21467,8 @@
       <c r="AD42" s="70"/>
     </row>
     <row r="43" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="199"/>
-      <c r="B43" s="194">
+      <c r="A43" s="198"/>
+      <c r="B43" s="196">
         <f>Neu!B24</f>
         <v>0</v>
       </c>
@@ -21503,7 +21503,7 @@
     </row>
     <row r="44" spans="1:30" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="114"/>
-      <c r="B44" s="196"/>
+      <c r="B44" s="199"/>
       <c r="C44" s="131"/>
       <c r="D44" s="132"/>
       <c r="E44" s="132"/>
@@ -22495,6 +22495,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A1:B2"/>
@@ -22511,14 +22519,6 @@
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="B3 B5 B7 B9 B11 B13 B15 B17 B19 B21 B23 B25 B27 B29 B31 B33 B35 B37 B39 B41 B43">
     <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
@@ -22572,35 +22572,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="198"/>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198" t="s">
+      <c r="A1" s="197"/>
+      <c r="B1" s="197"/>
+      <c r="C1" s="197" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="198"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="198"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="198"/>
-      <c r="O1" s="198"/>
-      <c r="P1" s="198"/>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
     </row>
     <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="198"/>
-      <c r="B2" s="198"/>
+      <c r="A2" s="197"/>
+      <c r="B2" s="197"/>
       <c r="C2" s="135" t="str">
         <f>Neu!$B4</f>
         <v>B4</v>
@@ -22687,10 +22687,10 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="199" t="s">
+      <c r="A3" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="197" t="str">
+      <c r="B3" s="194" t="str">
         <f>Neu!B4</f>
         <v>B4</v>
       </c>
@@ -22738,7 +22738,7 @@
       <c r="AD3" s="70"/>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="199"/>
+      <c r="A4" s="198"/>
       <c r="B4" s="195"/>
       <c r="C4" s="138"/>
       <c r="D4" s="103"/>
@@ -22775,8 +22775,8 @@
       <c r="AD4" s="70"/>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="199"/>
-      <c r="B5" s="194" t="str">
+      <c r="A5" s="198"/>
+      <c r="B5" s="196" t="str">
         <f>Neu!B5</f>
         <v>B8</v>
       </c>
@@ -22813,7 +22813,7 @@
       <c r="AD5" s="70"/>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="199"/>
+      <c r="A6" s="198"/>
       <c r="B6" s="195"/>
       <c r="C6" s="136"/>
       <c r="D6" s="119"/>
@@ -22848,8 +22848,8 @@
       <c r="AD6" s="70"/>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="199"/>
-      <c r="B7" s="194" t="str">
+      <c r="A7" s="198"/>
+      <c r="B7" s="196" t="str">
         <f>Neu!B6</f>
         <v>B20</v>
       </c>
@@ -22890,7 +22890,7 @@
       <c r="AD7" s="70"/>
     </row>
     <row r="8" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="199"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="195"/>
       <c r="C8" s="136">
         <v>0</v>
@@ -22929,8 +22929,8 @@
       <c r="AD8" s="70"/>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="199"/>
-      <c r="B9" s="194" t="str">
+      <c r="A9" s="198"/>
+      <c r="B9" s="196" t="str">
         <f>Neu!B7</f>
         <v>B30</v>
       </c>
@@ -22975,7 +22975,7 @@
       <c r="AD9" s="70"/>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="199"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="195"/>
       <c r="C10" s="136"/>
       <c r="D10" s="103">
@@ -23014,8 +23014,8 @@
       <c r="AD10" s="70"/>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="199"/>
-      <c r="B11" s="194" t="str">
+      <c r="A11" s="198"/>
+      <c r="B11" s="196" t="str">
         <f>Neu!B8</f>
         <v>B31s</v>
       </c>
@@ -23052,7 +23052,7 @@
       <c r="AD11" s="70"/>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="199"/>
+      <c r="A12" s="198"/>
       <c r="B12" s="195"/>
       <c r="C12" s="137"/>
       <c r="D12" s="118"/>
@@ -23087,8 +23087,8 @@
       <c r="AD12" s="70"/>
     </row>
     <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="199"/>
-      <c r="B13" s="194" t="str">
+      <c r="A13" s="198"/>
+      <c r="B13" s="196" t="str">
         <f>Neu!B9</f>
         <v>B31a</v>
       </c>
@@ -23127,7 +23127,7 @@
       <c r="AD13" s="70"/>
     </row>
     <row r="14" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="199"/>
+      <c r="A14" s="198"/>
       <c r="B14" s="195"/>
       <c r="C14" s="136"/>
       <c r="D14" s="103"/>
@@ -23164,8 +23164,8 @@
       <c r="AD14" s="70"/>
     </row>
     <row r="15" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="199"/>
-      <c r="B15" s="194" t="str">
+      <c r="A15" s="198"/>
+      <c r="B15" s="196" t="str">
         <f>Neu!B10</f>
         <v>B34</v>
       </c>
@@ -23212,7 +23212,7 @@
       <c r="AD15" s="70"/>
     </row>
     <row r="16" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="199"/>
+      <c r="A16" s="198"/>
       <c r="B16" s="195"/>
       <c r="C16" s="136"/>
       <c r="D16" s="103">
@@ -23251,8 +23251,8 @@
       <c r="AD16" s="70"/>
     </row>
     <row r="17" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="199"/>
-      <c r="B17" s="194" t="str">
+      <c r="A17" s="198"/>
+      <c r="B17" s="196" t="str">
         <f>Neu!B11</f>
         <v>B35</v>
       </c>
@@ -23295,7 +23295,7 @@
       <c r="AD17" s="70"/>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="199"/>
+      <c r="A18" s="198"/>
       <c r="B18" s="195"/>
       <c r="C18" s="136">
         <v>20</v>
@@ -23334,8 +23334,8 @@
       <c r="AD18" s="70"/>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="199"/>
-      <c r="B19" s="194" t="str">
+      <c r="A19" s="198"/>
+      <c r="B19" s="196" t="str">
         <f>Neu!B12</f>
         <v>B40</v>
       </c>
@@ -23378,7 +23378,7 @@
       <c r="AD19" s="70"/>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="199"/>
+      <c r="A20" s="198"/>
       <c r="B20" s="195"/>
       <c r="C20" s="136"/>
       <c r="D20" s="103">
@@ -23415,8 +23415,8 @@
       <c r="AD20" s="70"/>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="199"/>
-      <c r="B21" s="194" t="str">
+      <c r="A21" s="198"/>
+      <c r="B21" s="196" t="str">
         <f>Neu!B13</f>
         <v>B51s</v>
       </c>
@@ -23453,7 +23453,7 @@
       <c r="AD21" s="70"/>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="199"/>
+      <c r="A22" s="198"/>
       <c r="B22" s="195"/>
       <c r="C22" s="136"/>
       <c r="D22" s="103"/>
@@ -23488,8 +23488,8 @@
       <c r="AD22" s="70"/>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="199"/>
-      <c r="B23" s="194" t="str">
+      <c r="A23" s="198"/>
+      <c r="B23" s="196" t="str">
         <f>Neu!B14</f>
         <v>B51a</v>
       </c>
@@ -23532,7 +23532,7 @@
       <c r="AD23" s="70"/>
     </row>
     <row r="24" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="199"/>
+      <c r="A24" s="198"/>
       <c r="B24" s="195"/>
       <c r="C24" s="137"/>
       <c r="D24" s="118"/>
@@ -23567,8 +23567,8 @@
       <c r="AD24" s="70"/>
     </row>
     <row r="25" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="199"/>
-      <c r="B25" s="194" t="str">
+      <c r="A25" s="198"/>
+      <c r="B25" s="196" t="str">
         <f>Neu!B15</f>
         <v>B52</v>
       </c>
@@ -23611,7 +23611,7 @@
       <c r="AD25" s="70"/>
     </row>
     <row r="26" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="199"/>
+      <c r="A26" s="198"/>
       <c r="B26" s="195"/>
       <c r="C26" s="136"/>
       <c r="D26" s="103"/>
@@ -23648,8 +23648,8 @@
       <c r="AD26" s="70"/>
     </row>
     <row r="27" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="199"/>
-      <c r="B27" s="194" t="str">
+      <c r="A27" s="198"/>
+      <c r="B27" s="196" t="str">
         <f>Neu!B16</f>
         <v>B63</v>
       </c>
@@ -23698,7 +23698,7 @@
       <c r="AD27" s="70"/>
     </row>
     <row r="28" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="199"/>
+      <c r="A28" s="198"/>
       <c r="B28" s="195"/>
       <c r="C28" s="136"/>
       <c r="D28" s="103"/>
@@ -23741,8 +23741,8 @@
       <c r="AD28" s="70"/>
     </row>
     <row r="29" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="199"/>
-      <c r="B29" s="194" t="str">
+      <c r="A29" s="198"/>
+      <c r="B29" s="196" t="str">
         <f>Neu!B17</f>
         <v>B64s</v>
       </c>
@@ -23779,7 +23779,7 @@
       <c r="AD29" s="70"/>
     </row>
     <row r="30" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="199"/>
+      <c r="A30" s="198"/>
       <c r="B30" s="195"/>
       <c r="C30" s="136"/>
       <c r="D30" s="103"/>
@@ -23814,8 +23814,8 @@
       <c r="AD30" s="70"/>
     </row>
     <row r="31" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="199"/>
-      <c r="B31" s="194" t="str">
+      <c r="A31" s="198"/>
+      <c r="B31" s="196" t="str">
         <f>Neu!B18</f>
         <v>B64a</v>
       </c>
@@ -23878,7 +23878,7 @@
       <c r="AD31" s="70"/>
     </row>
     <row r="32" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="199"/>
+      <c r="A32" s="198"/>
       <c r="B32" s="195"/>
       <c r="C32" s="136"/>
       <c r="D32" s="103"/>
@@ -23913,8 +23913,8 @@
       <c r="AD32" s="70"/>
     </row>
     <row r="33" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="199"/>
-      <c r="B33" s="194" t="str">
+      <c r="A33" s="198"/>
+      <c r="B33" s="196" t="str">
         <f>Neu!B19</f>
         <v>B65</v>
       </c>
@@ -23962,7 +23962,7 @@
       <c r="AD33" s="70"/>
     </row>
     <row r="34" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="199"/>
+      <c r="A34" s="198"/>
       <c r="B34" s="195"/>
       <c r="C34" s="136"/>
       <c r="D34" s="103">
@@ -24002,8 +24002,8 @@
       <c r="AD34" s="70"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="199"/>
-      <c r="B35" s="194" t="str">
+      <c r="A35" s="198"/>
+      <c r="B35" s="196" t="str">
         <f>Neu!B20</f>
         <v>CBI2</v>
       </c>
@@ -24045,7 +24045,7 @@
       <c r="AD35" s="70"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="199"/>
+      <c r="A36" s="198"/>
       <c r="B36" s="195"/>
       <c r="C36" s="137"/>
       <c r="D36" s="118">
@@ -24089,8 +24089,8 @@
       <c r="AD36" s="70"/>
     </row>
     <row r="37" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="199"/>
-      <c r="B37" s="194">
+      <c r="A37" s="198"/>
+      <c r="B37" s="196">
         <f>Neu!B21</f>
         <v>0</v>
       </c>
@@ -24124,7 +24124,7 @@
       <c r="AD37" s="70"/>
     </row>
     <row r="38" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="199"/>
+      <c r="A38" s="198"/>
       <c r="B38" s="195"/>
       <c r="C38" s="136"/>
       <c r="D38" s="103"/>
@@ -24156,8 +24156,8 @@
       <c r="AD38" s="70"/>
     </row>
     <row r="39" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="199"/>
-      <c r="B39" s="194">
+      <c r="A39" s="198"/>
+      <c r="B39" s="196">
         <f>Neu!B22</f>
         <v>0</v>
       </c>
@@ -24191,7 +24191,7 @@
       <c r="AD39" s="70"/>
     </row>
     <row r="40" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="199"/>
+      <c r="A40" s="198"/>
       <c r="B40" s="195"/>
       <c r="C40" s="136"/>
       <c r="D40" s="103"/>
@@ -24223,8 +24223,8 @@
       <c r="AD40" s="70"/>
     </row>
     <row r="41" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="199"/>
-      <c r="B41" s="194">
+      <c r="A41" s="198"/>
+      <c r="B41" s="196">
         <f>Neu!B23</f>
         <v>0</v>
       </c>
@@ -24258,7 +24258,7 @@
       <c r="AD41" s="70"/>
     </row>
     <row r="42" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="199"/>
+      <c r="A42" s="198"/>
       <c r="B42" s="195"/>
       <c r="C42" s="136"/>
       <c r="D42" s="103"/>
@@ -24290,8 +24290,8 @@
       <c r="AD42" s="70"/>
     </row>
     <row r="43" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="199"/>
-      <c r="B43" s="194">
+      <c r="A43" s="198"/>
+      <c r="B43" s="196">
         <f>Neu!B24</f>
         <v>0</v>
       </c>
@@ -24326,7 +24326,7 @@
     </row>
     <row r="44" spans="1:30" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="114"/>
-      <c r="B44" s="196"/>
+      <c r="B44" s="199"/>
       <c r="C44" s="140"/>
       <c r="D44" s="132"/>
       <c r="E44" s="132"/>
@@ -25318,6 +25318,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:A43"/>
@@ -25334,14 +25342,6 @@
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
   </mergeCells>
   <conditionalFormatting sqref="B3 B5 B7 B9 B11 B13 B15 B17 B19 B21 B23 B25 B27 B29 B31 B33 B35 B37 B39 B41 B43">
     <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
@@ -25419,8 +25419,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="198"/>
-      <c r="B1" s="198"/>
+      <c r="A1" s="197"/>
+      <c r="B1" s="197"/>
       <c r="C1" s="203" t="s">
         <v>4</v>
       </c>
@@ -25464,8 +25464,8 @@
       <c r="AJ1" s="200"/>
     </row>
     <row r="2" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="198"/>
-      <c r="B2" s="198"/>
+      <c r="A2" s="197"/>
+      <c r="B2" s="197"/>
       <c r="C2" s="135" t="str">
         <f>Neu!$B4</f>
         <v>B4</v>
@@ -25582,10 +25582,10 @@
       </c>
     </row>
     <row r="3" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="199" t="s">
+      <c r="A3" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="197" t="str">
+      <c r="B3" s="194" t="str">
         <f>Neu!B4</f>
         <v>B4</v>
       </c>
@@ -25644,7 +25644,7 @@
       <c r="AK3" s="71"/>
     </row>
     <row r="4" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="199"/>
+      <c r="A4" s="198"/>
       <c r="B4" s="195"/>
       <c r="C4" s="124"/>
       <c r="D4" s="118"/>
@@ -25684,8 +25684,8 @@
       <c r="AK4" s="71"/>
     </row>
     <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="199"/>
-      <c r="B5" s="194" t="str">
+      <c r="A5" s="198"/>
+      <c r="B5" s="196" t="str">
         <f>Neu!B5</f>
         <v>B8</v>
       </c>
@@ -25723,7 +25723,7 @@
       </c>
     </row>
     <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="199"/>
+      <c r="A6" s="198"/>
       <c r="B6" s="195"/>
       <c r="C6" s="128"/>
       <c r="D6" s="119"/>
@@ -25759,8 +25759,8 @@
       </c>
     </row>
     <row r="7" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="199"/>
-      <c r="B7" s="194" t="str">
+      <c r="A7" s="198"/>
+      <c r="B7" s="196" t="str">
         <f>Neu!B6</f>
         <v>B20</v>
       </c>
@@ -25811,7 +25811,7 @@
       </c>
     </row>
     <row r="8" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="199"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="195"/>
       <c r="C8" s="128">
         <v>25</v>
@@ -25869,8 +25869,8 @@
       </c>
     </row>
     <row r="9" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="199"/>
-      <c r="B9" s="194" t="str">
+      <c r="A9" s="198"/>
+      <c r="B9" s="196" t="str">
         <f>Neu!B7</f>
         <v>B30</v>
       </c>
@@ -25922,7 +25922,7 @@
       </c>
     </row>
     <row r="10" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="199"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="195"/>
       <c r="C10" s="128"/>
       <c r="D10" s="103">
@@ -25969,8 +25969,8 @@
       <c r="AL10" s="71"/>
     </row>
     <row r="11" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="199"/>
-      <c r="B11" s="194" t="str">
+      <c r="A11" s="198"/>
+      <c r="B11" s="196" t="str">
         <f>Neu!B8</f>
         <v>B31s</v>
       </c>
@@ -26014,7 +26014,7 @@
       </c>
     </row>
     <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="199"/>
+      <c r="A12" s="198"/>
       <c r="B12" s="195"/>
       <c r="C12" s="128"/>
       <c r="D12" s="103"/>
@@ -26050,8 +26050,8 @@
       </c>
     </row>
     <row r="13" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="199"/>
-      <c r="B13" s="194" t="str">
+      <c r="A13" s="198"/>
+      <c r="B13" s="196" t="str">
         <f>Neu!B9</f>
         <v>B31a</v>
       </c>
@@ -26109,7 +26109,7 @@
       </c>
     </row>
     <row r="14" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="199"/>
+      <c r="A14" s="198"/>
       <c r="B14" s="195"/>
       <c r="C14" s="128"/>
       <c r="D14" s="103"/>
@@ -26165,8 +26165,8 @@
       </c>
     </row>
     <row r="15" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="199"/>
-      <c r="B15" s="194" t="str">
+      <c r="A15" s="198"/>
+      <c r="B15" s="196" t="str">
         <f>Neu!B10</f>
         <v>B34</v>
       </c>
@@ -26214,7 +26214,7 @@
       </c>
     </row>
     <row r="16" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="199"/>
+      <c r="A16" s="198"/>
       <c r="B16" s="195"/>
       <c r="C16" s="129"/>
       <c r="D16" s="118">
@@ -26260,8 +26260,8 @@
       </c>
     </row>
     <row r="17" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="199"/>
-      <c r="B17" s="194" t="str">
+      <c r="A17" s="198"/>
+      <c r="B17" s="196" t="str">
         <f>Neu!B11</f>
         <v>B35</v>
       </c>
@@ -26311,7 +26311,7 @@
       </c>
     </row>
     <row r="18" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="199"/>
+      <c r="A18" s="198"/>
       <c r="B18" s="195"/>
       <c r="C18" s="128">
         <v>16</v>
@@ -26351,8 +26351,8 @@
       </c>
     </row>
     <row r="19" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="199"/>
-      <c r="B19" s="194" t="str">
+      <c r="A19" s="198"/>
+      <c r="B19" s="196" t="str">
         <f>Neu!B12</f>
         <v>B40</v>
       </c>
@@ -26396,7 +26396,7 @@
       </c>
     </row>
     <row r="20" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="199"/>
+      <c r="A20" s="198"/>
       <c r="B20" s="195"/>
       <c r="C20" s="128"/>
       <c r="D20" s="103">
@@ -26434,8 +26434,8 @@
       </c>
     </row>
     <row r="21" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="199"/>
-      <c r="B21" s="194" t="str">
+      <c r="A21" s="198"/>
+      <c r="B21" s="196" t="str">
         <f>Neu!B13</f>
         <v>B51s</v>
       </c>
@@ -26485,7 +26485,7 @@
       </c>
     </row>
     <row r="22" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="199"/>
+      <c r="A22" s="198"/>
       <c r="B22" s="195"/>
       <c r="C22" s="128"/>
       <c r="D22" s="103"/>
@@ -26521,8 +26521,8 @@
       </c>
     </row>
     <row r="23" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="199"/>
-      <c r="B23" s="194" t="str">
+      <c r="A23" s="198"/>
+      <c r="B23" s="196" t="str">
         <f>Neu!B14</f>
         <v>B51a</v>
       </c>
@@ -26566,7 +26566,7 @@
       </c>
     </row>
     <row r="24" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="199"/>
+      <c r="A24" s="198"/>
       <c r="B24" s="195"/>
       <c r="C24" s="129"/>
       <c r="D24" s="118"/>
@@ -26608,8 +26608,8 @@
       </c>
     </row>
     <row r="25" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="199"/>
-      <c r="B25" s="194" t="str">
+      <c r="A25" s="198"/>
+      <c r="B25" s="196" t="str">
         <f>Neu!B15</f>
         <v>B52</v>
       </c>
@@ -26659,7 +26659,7 @@
       </c>
     </row>
     <row r="26" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="199"/>
+      <c r="A26" s="198"/>
       <c r="B26" s="195"/>
       <c r="C26" s="128"/>
       <c r="D26" s="103"/>
@@ -26703,8 +26703,8 @@
       </c>
     </row>
     <row r="27" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="199"/>
-      <c r="B27" s="194" t="str">
+      <c r="A27" s="198"/>
+      <c r="B27" s="196" t="str">
         <f>Neu!B16</f>
         <v>B63</v>
       </c>
@@ -26757,7 +26757,7 @@
       </c>
     </row>
     <row r="28" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="199"/>
+      <c r="A28" s="198"/>
       <c r="B28" s="195"/>
       <c r="C28" s="128"/>
       <c r="D28" s="103"/>
@@ -26801,8 +26801,8 @@
       </c>
     </row>
     <row r="29" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="199"/>
-      <c r="B29" s="194" t="str">
+      <c r="A29" s="198"/>
+      <c r="B29" s="196" t="str">
         <f>Neu!B17</f>
         <v>B64s</v>
       </c>
@@ -26840,7 +26840,7 @@
       </c>
     </row>
     <row r="30" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="199"/>
+      <c r="A30" s="198"/>
       <c r="B30" s="195"/>
       <c r="C30" s="128"/>
       <c r="D30" s="103"/>
@@ -26885,8 +26885,8 @@
       </c>
     </row>
     <row r="31" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="199"/>
-      <c r="B31" s="194" t="str">
+      <c r="A31" s="198"/>
+      <c r="B31" s="196" t="str">
         <f>Neu!B18</f>
         <v>B64a</v>
       </c>
@@ -26950,7 +26950,7 @@
       </c>
     </row>
     <row r="32" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="199"/>
+      <c r="A32" s="198"/>
       <c r="B32" s="195"/>
       <c r="C32" s="129"/>
       <c r="D32" s="118"/>
@@ -26986,8 +26986,8 @@
       </c>
     </row>
     <row r="33" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="199"/>
-      <c r="B33" s="194" t="str">
+      <c r="A33" s="198"/>
+      <c r="B33" s="196" t="str">
         <f>Neu!B19</f>
         <v>B65</v>
       </c>
@@ -27045,7 +27045,7 @@
       </c>
     </row>
     <row r="34" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="199"/>
+      <c r="A34" s="198"/>
       <c r="B34" s="195"/>
       <c r="C34" s="128"/>
       <c r="D34" s="103">
@@ -27092,8 +27092,8 @@
       </c>
     </row>
     <row r="35" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="199"/>
-      <c r="B35" s="194" t="str">
+      <c r="A35" s="198"/>
+      <c r="B35" s="196" t="str">
         <f>Neu!B20</f>
         <v>CBI2</v>
       </c>
@@ -27142,7 +27142,7 @@
       </c>
     </row>
     <row r="36" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="199"/>
+      <c r="A36" s="198"/>
       <c r="B36" s="195"/>
       <c r="C36" s="128"/>
       <c r="D36" s="103">
@@ -27199,8 +27199,8 @@
       </c>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="199"/>
-      <c r="B37" s="194">
+      <c r="A37" s="198"/>
+      <c r="B37" s="196">
         <f>Neu!B21</f>
         <v>0</v>
       </c>
@@ -27247,7 +27247,7 @@
       </c>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="199"/>
+      <c r="A38" s="198"/>
       <c r="B38" s="195"/>
       <c r="C38" s="128"/>
       <c r="D38" s="103"/>
@@ -27285,8 +27285,8 @@
       </c>
     </row>
     <row r="39" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="199"/>
-      <c r="B39" s="194">
+      <c r="A39" s="198"/>
+      <c r="B39" s="196">
         <f>Neu!B22</f>
         <v>0</v>
       </c>
@@ -27329,7 +27329,7 @@
       </c>
     </row>
     <row r="40" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="199"/>
+      <c r="A40" s="198"/>
       <c r="B40" s="195"/>
       <c r="C40" s="128"/>
       <c r="D40" s="103"/>
@@ -27370,8 +27370,8 @@
       </c>
     </row>
     <row r="41" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="199"/>
-      <c r="B41" s="194">
+      <c r="A41" s="198"/>
+      <c r="B41" s="196">
         <f>Neu!B23</f>
         <v>0</v>
       </c>
@@ -27405,7 +27405,7 @@
       </c>
     </row>
     <row r="42" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="199"/>
+      <c r="A42" s="198"/>
       <c r="B42" s="195"/>
       <c r="C42" s="128"/>
       <c r="D42" s="103"/>
@@ -27438,8 +27438,8 @@
       </c>
     </row>
     <row r="43" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="199"/>
-      <c r="B43" s="194">
+      <c r="A43" s="198"/>
+      <c r="B43" s="196">
         <f>Neu!B24</f>
         <v>0</v>
       </c>
@@ -27475,7 +27475,7 @@
     </row>
     <row r="44" spans="1:36" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="114"/>
-      <c r="B44" s="196"/>
+      <c r="B44" s="199"/>
       <c r="C44" s="131"/>
       <c r="D44" s="132"/>
       <c r="E44" s="132"/>
@@ -28621,11 +28621,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C1:W1"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="A1:B2"/>
@@ -28642,12 +28643,11 @@
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C1:W1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3 B5 B7 B9 B11 B13 B15 B17 B19 B21 B23 B25 B27 B29 B31 B33 B35 B37 B39 B41 B43">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">

--- a/Excel_files/momohara_neveu_2021_control.xlsx
+++ b/Excel_files/momohara_neveu_2021_control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EABE534-99AE-4112-9025-25B9DA53AC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC25E08D-9377-47B3-9FC9-4A53AB02B583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" activeTab="6" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="716" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
@@ -10905,7 +10905,7 @@
       <c r="JN17" s="17"/>
       <c r="JO17" s="17"/>
       <c r="JP17" s="20"/>
-      <c r="JQ17" s="44">
+      <c r="JQ17" s="14">
         <v>0.35</v>
       </c>
       <c r="JR17" s="17">

--- a/Excel_files/momohara_neveu_2021_control.xlsx
+++ b/Excel_files/momohara_neveu_2021_control.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC25E08D-9377-47B3-9FC9-4A53AB02B583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A894649A-06E3-482A-B4BB-25C68204249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="716" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
